--- a/artfynd/A 47499-2023 artfynd.xlsx
+++ b/artfynd/A 47499-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47499-2023 artfynd.xlsx
+++ b/artfynd/A 47499-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17276184</v>
+        <v>103521597</v>
       </c>
       <c r="B2" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560432.8941751474</v>
+        <v>560156</v>
       </c>
       <c r="R2" t="n">
-        <v>6983650.668582294</v>
+        <v>6983638</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,40 +757,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Lövrik skog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17270843</v>
+        <v>103521619</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,19 +806,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560432.8941751474</v>
+        <v>560248</v>
       </c>
       <c r="R3" t="n">
-        <v>6983650.668582294</v>
+        <v>6983685</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +843,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,82 +859,65 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Lövrik skog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17276181</v>
+        <v>103521603</v>
       </c>
       <c r="B4" t="n">
-        <v>98493</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bodflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560432.8941751474</v>
+        <v>560156</v>
       </c>
       <c r="R4" t="n">
-        <v>6983650.668582294</v>
+        <v>6983638</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +941,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,40 +957,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Lövrik skog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17270825</v>
+        <v>103521614</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,41 +984,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560432.8941751474</v>
+        <v>560248</v>
       </c>
       <c r="R5" t="n">
-        <v>6983650.668582294</v>
+        <v>6983685</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,22 +1039,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,24 +1055,455 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Lövrik skog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>17276181</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bodflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>560433</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6983651</v>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lövrik skog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Caroline Westerlund</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Via Caroline Westerlund</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>17270843</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bodflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>560433</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6983651</v>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Lövrik skog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>17270825</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bodflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>560433</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6983651</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Lövrik skog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>17276184</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bodflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>560433</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6983651</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Lövrik skog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 47499-2023 artfynd.xlsx
+++ b/artfynd/A 47499-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103521597</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103521619</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -970,6 +985,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103521603</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103521614</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17276181</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270843</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1398,6 +1433,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270825</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,8 +1548,23 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17276184</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 47499-2023 artfynd.xlsx
+++ b/artfynd/A 47499-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1211,52 +1211,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17270843</v>
+        <v>136332257</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>101486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bodflon, Jmt</t>
+          <t>Ansjöån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560433</v>
+        <v>560511</v>
       </c>
       <c r="R7" t="n">
-        <v>6983651</v>
+        <v>6983716</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,12 +1276,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,82 +1292,69 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Lövrik skog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17270843</t>
+          <t>https://artportalen.se/Sighting/136332257</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17270825</v>
+        <v>136332247</v>
       </c>
       <c r="B8" t="n">
-        <v>80432</v>
+        <v>97413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bodflon, Jmt</t>
+          <t>Ansjöån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560433</v>
+        <v>560342</v>
       </c>
       <c r="R8" t="n">
-        <v>6983651</v>
+        <v>6983771</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1395,12 +1378,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,62 +1394,53 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Lövrik skog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17270825</t>
+          <t>https://artportalen.se/Sighting/136332247</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17276184</v>
+        <v>17270843</v>
       </c>
       <c r="B9" t="n">
-        <v>99022</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1549,6 +1523,236 @@
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270843</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>17270825</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bodflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>560433</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6983651</v>
+      </c>
+      <c r="S10" t="n">
+        <v>100</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Lövrik skog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270825</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>17276184</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bodflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>560433</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6983651</v>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Lövrik skog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/17276184</t>
         </is>
@@ -1564,6 +1768,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
